--- a/tests/testdata/excel/大文字拡張子.XLSX
+++ b/tests/testdata/excel/大文字拡張子.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BD568EE-76EA-411C-89F4-7A7F4C982DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E21327-9504-44B9-B2F9-6F702D654AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{8C4808C2-C776-49D4-87DB-6BF160C2A382}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{3C3BCB53-2F29-41A2-B4C9-3F9D992CA937}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DB1564-6A1E-4E78-B23B-536D81C987BC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56533E9-4A9E-4384-A3E3-39559F780C75}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/大文字拡張子.XLSX
+++ b/tests/testdata/excel/大文字拡張子.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90E21327-9504-44B9-B2F9-6F702D654AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EFE58F8-CAEA-45A1-8D7F-711B68E76361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{3C3BCB53-2F29-41A2-B4C9-3F9D992CA937}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{5504243B-8FDC-483F-B886-944AD94E5D26}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C56533E9-4A9E-4384-A3E3-39559F780C75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63BA93C6-E3D4-4543-A0F8-04A08219E17F}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
